--- a/public/post/drafts/season-prediction/johaug.xlsx
+++ b/public/post/drafts/season-prediction/johaug.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -20,19 +20,25 @@
     <t xml:space="preserve">Nation</t>
   </si>
   <si>
+    <t xml:space="preserve">Season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
     <t xml:space="preserve">Predicted Points</t>
   </si>
   <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
     <t xml:space="preserve">Elo</t>
   </si>
   <si>
     <t xml:space="preserve">Distance Elo</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint Elo</t>
+    <t xml:space="preserve">Distance Classic Elo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance Freestyle Elo</t>
   </si>
   <si>
     <t xml:space="preserve">Therese Johaug</t>
@@ -41,7 +47,28 @@
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
+    <t xml:space="preserve">33.71115674195756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7111567419576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.644163975309308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7111567419576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.644002027314544</t>
+  </si>
+  <si>
     <t xml:space="preserve">36.7111567419576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621032324652448</t>
   </si>
 </sst>
 </file>
@@ -392,28 +419,127 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.625173065648618</v>
+        <v>2022</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1880.5390984927</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1895.96952462862</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1766.63388642515</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1716.41485230943</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
-        <v>1802.85931104148</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1818.28973717741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1484.32342611202</v>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1847.85678902402</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1863.01904633398</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1749.88866930781</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1699.48922426858</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1833.81415507832</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1848.8611880752</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1739.72403851565</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1689.31225632476</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1791.26716003053</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1805.96508129402</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1708.91990687742</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1664.41002777073</v>
       </c>
     </row>
   </sheetData>
